--- a/app/reports/SIGA_research.xlsx
+++ b/app/reports/SIGA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.05</v>
+        <v>2.885</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699999809265137</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>71724097.04918033</v>
+        <v>71724095.66724437</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>3.05</v>
+        <v>2.885</v>
       </c>
     </row>
     <row r="38">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>218758496</v>
+        <v>206924016</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>494339968</v>
+        <v>564588928</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
@@ -1552,14 +1552,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>753931520</v>
+        <v>741947072</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-6.431</v>
+        <v>-4.98</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>10.968</v>
+        <v>23.458</v>
       </c>
     </row>
     <row r="8">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>71171048</v>
+        <v>69854864</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>248162960</v>
+        <v>227909984</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1052537024</v>
+        <v>1045549248</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>239334656</v>
+        <v>242551520</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>750370112</v>
+        <v>765314048</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>2.3783305</v>
+        <v>2.425696</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>7.748</v>

--- a/app/reports/SIGA_research.xlsx
+++ b/app/reports/SIGA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.885</v>
+        <v>2.895</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04699999809265137</v>
+        <v>0.04684000015258789</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>71724095.66724437</v>
+        <v>71849710.53540587</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.885</v>
+        <v>2.895</v>
       </c>
     </row>
     <row r="38">
@@ -1508,14 +1508,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>206924016</v>
+        <v>208004912</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-9.67</v>
+        <v>-8.85</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="6">
@@ -1530,14 +1530,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>564588928</v>
+        <v>575266176</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-7.718</v>
+        <v>-8.510999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>8.496</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1552,14 +1552,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>741947072</v>
+        <v>755020992</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-4.98</v>
+        <v>-4.93</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>23.458</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="8">
@@ -1574,14 +1574,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>69854864</v>
+        <v>78190656</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-2.028</v>
+        <v>-2.109</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.076</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -1596,14 +1596,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>227909984</v>
+        <v>228166336</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>2.998</v>
+        <v>2.916</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.905</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="10">
@@ -1640,11 +1640,11 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>1045549248</v>
+        <v>909723904</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-2.881</v>
+        <v>-2.788</v>
       </c>
       <c r="F11" s="33" t="n"/>
     </row>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>242551520</v>
+        <v>234187680</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>765314048</v>
+        <v>775214336</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>2.425696</v>
+        <v>2.4570754</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>7.748</v>
+        <v>8.058</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>2.511</v>
+        <v>2.612</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SIGA_research.xlsx
+++ b/app/reports/SIGA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.895</v>
+        <v>2.9</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04644999980926514</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>71849710.53540587</v>
+        <v>71849715.86206897</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.895</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="38">
@@ -1508,14 +1508,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>208004912</v>
+        <v>208364176</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-8.85</v>
+        <v>-8.44</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="6">
@@ -1530,14 +1530,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>575266176</v>
+        <v>543465408</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-8.510999999999999</v>
+        <v>-8.782999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>9.369999999999999</v>
+        <v>9.669</v>
       </c>
     </row>
     <row r="7">
@@ -1552,14 +1552,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>755020992</v>
+        <v>744126016</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-4.93</v>
+        <v>-5.056</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>23.22</v>
+        <v>23.815</v>
       </c>
     </row>
     <row r="8">
@@ -1574,14 +1574,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>78190656</v>
+        <v>73900888</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-2.109</v>
+        <v>-3.088</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.2</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="9">
@@ -1596,14 +1596,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>228166336</v>
+        <v>237139184</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>2.916</v>
+        <v>2.934</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.88</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="10">
@@ -1640,11 +1640,11 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>909723904</v>
+        <v>915224960</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-2.788</v>
+        <v>-2.067</v>
       </c>
       <c r="F11" s="33" t="n"/>
     </row>
@@ -1660,14 +1660,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>234187680</v>
+        <v>233544304</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-41.238</v>
+        <v>-40.575</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.875</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="13">
@@ -1682,16 +1682,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>775214336</v>
+        <v>754292928</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>2.4570754</v>
+        <v>2.3978622</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>8.058</v>
+        <v>8.102</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>2.612</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="15">
